--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2995,6 +2995,340 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128338074</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>575436</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6509768</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128338706</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skärgölen, Skärgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>575696</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6509992</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128337259</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>575323</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6509823</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3121,7 +3121,7 @@
         <v>128338706</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3000,7 +3000,7 @@
         <v>128338074</v>
       </c>
       <c r="B24" t="n">
-        <v>56867</v>
+        <v>56879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>128338706</v>
       </c>
       <c r="B25" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3000,7 +3000,7 @@
         <v>128338074</v>
       </c>
       <c r="B24" t="n">
-        <v>56879</v>
+        <v>56883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>128338706</v>
       </c>
       <c r="B25" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3000,7 +3000,7 @@
         <v>128338074</v>
       </c>
       <c r="B24" t="n">
-        <v>56883</v>
+        <v>56910</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>128338706</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -3000,7 +3000,7 @@
         <v>128338074</v>
       </c>
       <c r="B24" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>128338706</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>128337259</v>
       </c>
       <c r="B26" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -2082,12 +2082,7 @@
         <v>114459114</v>
       </c>
       <c r="B15" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,6 +2108,14 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norr om Lilla Äljsjön, Ög</t>
@@ -2163,6 +2166,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2184,12 +2188,7 @@
         <v>114459115</v>
       </c>
       <c r="B16" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,6 +2214,14 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norr om Lilla Äljsjön, Ög</t>
@@ -2265,6 +2272,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2694,12 +2702,7 @@
         <v>114459109</v>
       </c>
       <c r="B21" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,6 +2728,15 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Norr om Lilla Äljsjön, Ög</t>
@@ -2796,12 +2808,7 @@
         <v>114459110</v>
       </c>
       <c r="B22" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,6 +2834,15 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Norr om Lilla Äljsjön, Ög</t>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -2702,7 +2702,7 @@
         <v>114459109</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>114459110</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111747186</v>
+        <v>111749097</v>
       </c>
       <c r="B2" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla gruvan (Lilla gruvan), Ög</t>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575436</v>
+        <v>575501</v>
       </c>
       <c r="R2" t="n">
-        <v>6509857</v>
+        <v>6509776</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111747705</v>
+        <v>111964621</v>
       </c>
       <c r="B3" t="n">
-        <v>93067</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,38 +784,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla gruvan (Lilla gruvan), Ög</t>
+          <t>Stenstorp SSO 1660 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575459</v>
+        <v>575609</v>
       </c>
       <c r="R3" t="n">
-        <v>6509864</v>
+        <v>6509825</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,72 +856,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111749860</v>
+        <v>114459119</v>
       </c>
       <c r="B4" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgsjöhåll (Älgsjöhåll), Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575357</v>
+        <v>575616</v>
       </c>
       <c r="R4" t="n">
-        <v>6509772</v>
+        <v>6509827</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,66 +965,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111749897</v>
+        <v>114459120</v>
       </c>
       <c r="B5" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älgsjöhåll (Älgsjöhåll), Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575337</v>
+        <v>575469</v>
       </c>
       <c r="R5" t="n">
-        <v>6509781</v>
+        <v>6509896</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,66 +1062,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111749883</v>
+        <v>111747705</v>
       </c>
       <c r="B6" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgsjöhåll (Älgsjöhåll), Ög</t>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575337</v>
+        <v>575459</v>
       </c>
       <c r="R6" t="n">
-        <v>6509789</v>
+        <v>6509864</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,54 +1172,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111749097</v>
+        <v>114459116</v>
       </c>
       <c r="B7" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla gruvan (Lilla gruvan), Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575502</v>
+        <v>575404</v>
       </c>
       <c r="R7" t="n">
-        <v>6509776</v>
+        <v>6509935</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,66 +1257,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111749006</v>
+        <v>114459117</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla gruvan (Lilla gruvan), Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575512</v>
+        <v>575379</v>
       </c>
       <c r="R8" t="n">
-        <v>6509826</v>
+        <v>6509946</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,27 +1354,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111749343</v>
+        <v>114459118</v>
       </c>
       <c r="B9" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,38 +1377,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla gruvan (Lilla gruvan), Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575415</v>
+        <v>575277</v>
       </c>
       <c r="R9" t="n">
-        <v>6509808</v>
+        <v>6509778</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,12 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,81 +1451,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111964550</v>
+        <v>128337259</v>
       </c>
       <c r="B10" t="n">
-        <v>103781</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenstorp SSO 1470 m, Ög</t>
+          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575346</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>6509958</v>
+        <v>6509823</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1585,12 +1528,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,81 +1542,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111964621</v>
+        <v>114459108</v>
       </c>
       <c r="B11" t="n">
-        <v>93553</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenstorp SSO 1660 m, Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575609</v>
+        <v>575547</v>
       </c>
       <c r="R11" t="n">
-        <v>6509825</v>
+        <v>6509858</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1697,12 +1625,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,39 +1639,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111964494</v>
+        <v>111747186</v>
       </c>
       <c r="B12" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,49 +1668,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenstorp SSO 1470 m, Ög</t>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575346</v>
+        <v>575436</v>
       </c>
       <c r="R12" t="n">
-        <v>6509958</v>
+        <v>6509857</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,22 +1723,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,36 +1739,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113027577</v>
+        <v>111749343</v>
       </c>
       <c r="B13" t="n">
-        <v>56781</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1880,38 +1766,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla gruvan (Lilla gruvan), Ög</t>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575588</v>
+        <v>575415</v>
       </c>
       <c r="R13" t="n">
-        <v>6509904</v>
+        <v>6509808</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,22 +1821,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,65 +1841,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Jonsson, Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114459116</v>
+        <v>111749860</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575404</v>
+        <v>575357</v>
       </c>
       <c r="R14" t="n">
-        <v>6509935</v>
+        <v>6509772</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2047,12 +1919,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,68 +1939,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114459114</v>
+        <v>111749883</v>
       </c>
       <c r="B15" t="n">
-        <v>4779</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575673</v>
+        <v>575337</v>
       </c>
       <c r="R15" t="n">
-        <v>6509968</v>
+        <v>6509789</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2152,12 +2017,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,75 +2031,67 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114459115</v>
+        <v>111749897</v>
       </c>
       <c r="B16" t="n">
-        <v>4779</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575383</v>
+        <v>575337</v>
       </c>
       <c r="R16" t="n">
-        <v>6509946</v>
+        <v>6509781</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,12 +2115,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,34 +2129,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114459120</v>
+        <v>111964494</v>
       </c>
       <c r="B17" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,37 +2158,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Stenstorp SSO 1470 m, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575469</v>
+        <v>575346</v>
       </c>
       <c r="R17" t="n">
-        <v>6509896</v>
+        <v>6509958</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,12 +2224,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,31 +2250,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114459118</v>
+        <v>113027577</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,37 +2282,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575277</v>
+        <v>575588</v>
       </c>
       <c r="R18" t="n">
-        <v>6509778</v>
+        <v>6509904</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2466,9 +2340,19 @@
           <t>2023-11-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,27 +2367,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114459119</v>
+        <v>128338706</v>
       </c>
       <c r="B19" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,37 +2390,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Skärgölen, Skärgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575616</v>
+        <v>575696</v>
       </c>
       <c r="R19" t="n">
-        <v>6509827</v>
+        <v>6509992</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2565,12 +2453,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,27 +2483,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114459117</v>
+        <v>114459114</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,34 +2506,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575379</v>
+        <v>575673</v>
       </c>
       <c r="R20" t="n">
-        <v>6509946</v>
+        <v>6509968</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2681,6 +2582,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114459109</v>
+        <v>114459115</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>4781</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,30 +2612,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2743,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575557</v>
+        <v>575383</v>
       </c>
       <c r="R21" t="n">
-        <v>6509801</v>
+        <v>6509946</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2787,6 +2688,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114459110</v>
+        <v>128337521</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>57144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,46 +2718,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575569</v>
+        <v>575303</v>
       </c>
       <c r="R22" t="n">
-        <v>6509925</v>
+        <v>6509954</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2879,12 +2781,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,62 +2811,71 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114459108</v>
+        <v>128338074</v>
       </c>
       <c r="B23" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norr om Lilla Äljsjön, Ög</t>
+          <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575547</v>
+        <v>575436</v>
       </c>
       <c r="R23" t="n">
-        <v>6509858</v>
+        <v>6509768</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2981,12 +2902,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3001,22 +2932,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128338074</v>
+        <v>111749006</v>
       </c>
       <c r="B24" t="n">
-        <v>56913</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,51 +2955,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilla gruvan, Lilla gruvan, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575436</v>
+        <v>575512</v>
       </c>
       <c r="R24" t="n">
-        <v>6509768</v>
+        <v>6509826</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3092,22 +3010,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3122,69 +3030,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128338706</v>
+        <v>114459109</v>
       </c>
       <c r="B25" t="n">
-        <v>57717</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skärgölen, Skärgölen, Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575696</v>
+        <v>575557</v>
       </c>
       <c r="R25" t="n">
-        <v>6509992</v>
+        <v>6509801</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3208,22 +3116,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,57 +3136,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128337259</v>
+        <v>114459110</v>
       </c>
       <c r="B26" t="n">
-        <v>91528</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Älgsjöhåll, Älgsjöhåll, Ög</t>
+          <t>Norr om Lilla Äljsjön, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575323</v>
+        <v>575569</v>
       </c>
       <c r="R26" t="n">
-        <v>6509823</v>
+        <v>6509925</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3315,12 +3222,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,15 +3242,237 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>111964550</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenstorp SSO 1470 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>575346</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6509958</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111964753</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100961</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>224841</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vanlig kavelhirs</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Setaria viridis var. viridis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenstorp SSO 1730 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>575561</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6509765</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Grushög</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34644-2023 artfynd.xlsx
+++ b/artfynd/A 34644-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111749097</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459119</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459120</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111747705</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459116</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459117</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459118</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128337259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459108</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111747186</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111749343</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111749860</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111749883</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2144,6 +2219,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111749897</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964494</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113027577</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128338706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2598,6 +2693,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459114</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2704,6 +2804,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459115</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128337521</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128338074</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3039,6 +3154,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111749006</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3145,6 +3265,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459109</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3251,6 +3376,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459110</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3370,6 +3500,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964550</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3473,8 +3608,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>